--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.01_Q4_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.01_Q4_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0009333390227496771</v>
+        <v>0.000226662781988474</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009333390227496771</v>
+        <v>0.000226662781988474</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007474015486001477</v>
+        <v>0.0003267535918220852</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0009168845588968523</v>
+        <v>0.000222950327083341</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009168845588968523</v>
+        <v>0.000222950327083341</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007732197877945703</v>
+        <v>0.0003300105832023972</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0009186428671939103</v>
+        <v>0.0002232528662429692</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0009186428671939103</v>
+        <v>0.0002232528662429692</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007502810051043589</v>
+        <v>0.0003254970745037421</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0009182215273480203</v>
+        <v>0.0002228365296824322</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009182215273480203</v>
+        <v>0.0002228365296824322</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0007330033767427357</v>
+        <v>0.0003230370572983564</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0009103164437956003</v>
+        <v>0.0002204998764110631</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009103164437956003</v>
+        <v>0.0002204998764110631</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0007126829060575507</v>
+        <v>0.000321266431149402</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0009042243190443188</v>
+        <v>0.000218561005603021</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0009042243190443188</v>
+        <v>0.000218561005603021</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0006895423958964543</v>
+        <v>0.0003177364302346984</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0008931181881537431</v>
+        <v>0.0002153660724548341</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0008931181881537431</v>
+        <v>0.0002153660724548341</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0006671582053627591</v>
+        <v>0.0003141820183666379</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0008809909052055751</v>
+        <v>0.0002119149866528629</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0008809909052055751</v>
+        <v>0.0002119149866528629</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0006450465598939882</v>
+        <v>0.0003102813400886479</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0008681116095984993</v>
+        <v>0.0002082949267075208</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0008681116095984993</v>
+        <v>0.0002082949267075208</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000623785892713943</v>
+        <v>0.0003058920894450152</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.00085505175501589</v>
+        <v>0.0002046895947984736</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00085505175501589</v>
+        <v>0.0002046895947984736</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0006034613155258547</v>
+        <v>0.0003011548695117445</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0008425276240931299</v>
+        <v>0.0002012334395181563</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0008425276240931299</v>
+        <v>0.0002012334395181563</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0005844500289477147</v>
+        <v>0.0002960992932798939</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0008310552379647357</v>
+        <v>0.0001981159164775046</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0008310552379647357</v>
+        <v>0.0001981159164775046</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0005668647555835756</v>
+        <v>0.0002910565852506152</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0008211124339078417</v>
+        <v>0.0001954407079834023</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0008211124339078417</v>
+        <v>0.0001954407079834023</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0005509261079692326</v>
+        <v>0.0002861781153122864</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0008128742248498962</v>
+        <v>0.0001932501955180102</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0008128742248498962</v>
+        <v>0.0001932501955180102</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0005368048708196358</v>
+        <v>0.0002817034919517145</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0008064325176830661</v>
+        <v>0.0001915643198353314</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0008064325176830661</v>
+        <v>0.0001915643198353314</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0005244879306220068</v>
+        <v>0.0002775219055258225</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.000801924926553137</v>
+        <v>0.0001904135063741615</v>
       </c>
       <c r="C17" t="n">
-        <v>0.000801924926553137</v>
+        <v>0.0001904135063741615</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0005144097585007888</v>
+        <v>0.0002738861764537461</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0007996071721332093</v>
+        <v>0.0001898570679054272</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0007996071721332093</v>
+        <v>0.0001898570679054272</v>
       </c>
       <c r="D18" t="n">
-        <v>0.000506016165006024</v>
+        <v>0.0002712090264040739</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0007997952374373869</v>
+        <v>0.0001899685632545614</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0007997952374373869</v>
+        <v>0.0001899685632545614</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0005003469463802352</v>
+        <v>0.0002693881049636518</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0008028023471412919</v>
+        <v>0.000190820636112643</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0008028023471412919</v>
+        <v>0.000190820636112643</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0004971334350026825</v>
+        <v>0.000268760034650388</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.000808831604255534</v>
+        <v>0.0001924565268791129</v>
       </c>
       <c r="C21" t="n">
-        <v>0.000808831604255534</v>
+        <v>0.0001924565268791129</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0004977860374803842</v>
+        <v>0.0002696516186336632</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.0008181894206230829</v>
+        <v>0.0001949498619263677</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0008181894206230829</v>
+        <v>0.0001949498619263677</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0005014656033858246</v>
+        <v>0.0002715783894542062</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.0008309908361737851</v>
+        <v>0.0001983245475207787</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0008309908361737851</v>
+        <v>0.0001983245475207787</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0005082940246685935</v>
+        <v>0.0002753260100121637</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0008473602777392602</v>
+        <v>0.0002021075463490719</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0008473602777392602</v>
+        <v>0.0002021075463490719</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0005185231458768174</v>
+        <v>0.0002805513359224075</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.0008647985260380221</v>
+        <v>0.0002071627519320312</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0008647985260380221</v>
+        <v>0.0002071627519320312</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0005324778631170264</v>
+        <v>0.0002878870917420178</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.000888244745051236</v>
+        <v>0.0002132308504984273</v>
       </c>
       <c r="C26" t="n">
-        <v>0.000888244745051236</v>
+        <v>0.0002132308504984273</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0005490182342646789</v>
+        <v>0.0002963451990039662</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.0009159407695510867</v>
+        <v>0.0002203517750119611</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0009159407695510867</v>
+        <v>0.0002203517750119611</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0005688436691601492</v>
+        <v>0.0003068270172058048</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.0009480248221048139</v>
+        <v>0.0002285661653756595</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0009480248221048139</v>
+        <v>0.0002285661653756595</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0005917037972288433</v>
+        <v>0.000319270737956071</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.0009846208699506285</v>
+        <v>0.0002378997647069283</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0009846208699506285</v>
+        <v>0.0002378997647069283</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0006167856625120409</v>
+        <v>0.0003330771446572594</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.001025799404688161</v>
+        <v>0.0002483681827531418</v>
       </c>
       <c r="C30" t="n">
-        <v>0.001025799404688161</v>
+        <v>0.0002483681827531418</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0006443974456576491</v>
+        <v>0.0003483774401790558</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.001071606784984504</v>
+        <v>0.0002599799284344236</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001071606784984504</v>
+        <v>0.0002599799284344236</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0006740439372306767</v>
+        <v>0.0003653179528642755</v>
       </c>
     </row>
   </sheetData>
